--- a/data/greenfee-prices.xlsx
+++ b/data/greenfee-prices.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="35">
   <si>
     <t>BELKA GOLF — Green Fee Fiyat Tablosu (Doldurma Şablonu)</t>
   </si>
@@ -118,6 +118,18 @@
   </si>
   <si>
     <t xml:space="preserve">(SOR)Special Offer Rate (€) </t>
+  </si>
+  <si>
+    <t>All Inclusive</t>
+  </si>
+  <si>
+    <t>evet</t>
+  </si>
+  <si>
+    <t>hayır</t>
+  </si>
+  <si>
+    <t>Token</t>
   </si>
 </sst>
 </file>
@@ -263,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -287,17 +299,24 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -609,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -618,27 +637,29 @@
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
     <col min="6" max="6" width="10.85546875" customWidth="1"/>
     <col min="8" max="8" width="12.140625" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" customWidth="1"/>
-    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:12" ht="18">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-    </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+    </row>
+    <row r="2" spans="1:12" ht="30" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-    </row>
-    <row r="4" spans="1:10" ht="30" customHeight="1">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+    </row>
+    <row r="4" spans="1:12" ht="30" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -651,22 +672,28 @@
       <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="9" t="s">
+      <c r="F4" s="15"/>
+      <c r="G4" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="16"/>
-      <c r="I4" s="8" t="s">
+      <c r="H4" s="19"/>
+      <c r="I4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L4" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -679,20 +706,24 @@
       <c r="D5" s="3">
         <v>110</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="11">
+      <c r="E5" s="12"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="12">
         <v>100</v>
       </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="7">
+      <c r="H5" s="13"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="7">
         <v>60</v>
       </c>
-      <c r="J5" s="7">
+      <c r="K5" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L5" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -705,20 +736,24 @@
       <c r="D6" s="3">
         <v>145</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="11">
+      <c r="E6" s="12"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="12">
         <v>105</v>
       </c>
-      <c r="H6" s="12"/>
-      <c r="I6" s="7">
+      <c r="H6" s="13"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="7">
         <v>60</v>
       </c>
-      <c r="J6" s="7">
+      <c r="K6" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L6" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -731,20 +766,24 @@
       <c r="D7" s="3">
         <v>195</v>
       </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="11">
+      <c r="E7" s="12"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="12">
         <v>170</v>
       </c>
-      <c r="H7" s="12"/>
-      <c r="I7" s="7">
+      <c r="H7" s="13"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="7">
         <v>60</v>
       </c>
-      <c r="J7" s="7">
+      <c r="K7" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L7" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="14.25" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
@@ -757,20 +796,24 @@
       <c r="D8" s="3">
         <v>110</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="11">
+      <c r="E8" s="12"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="12">
         <v>100</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="7">
+      <c r="H8" s="13"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="7">
         <v>60</v>
       </c>
-      <c r="J8" s="7">
+      <c r="K8" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L8" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
@@ -783,20 +826,24 @@
       <c r="D9" s="3">
         <v>195</v>
       </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="11">
+      <c r="E9" s="12"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="12">
         <v>170</v>
       </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="7">
+      <c r="H9" s="13"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="7">
         <v>60</v>
       </c>
-      <c r="J9" s="7">
+      <c r="K9" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L9" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
@@ -809,20 +856,24 @@
       <c r="D10" s="3">
         <v>145</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="11">
+      <c r="E10" s="12"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="12">
         <v>105</v>
       </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="7">
+      <c r="H10" s="13"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="7">
         <v>60</v>
       </c>
-      <c r="J10" s="7">
+      <c r="K10" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L10" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="14.25" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
@@ -835,20 +886,24 @@
       <c r="D11" s="3">
         <v>110</v>
       </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="11">
+      <c r="E11" s="12"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="12">
         <v>100</v>
       </c>
-      <c r="H11" s="12"/>
-      <c r="I11" s="7">
+      <c r="H11" s="13"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="7">
         <v>60</v>
       </c>
-      <c r="J11" s="7">
+      <c r="K11" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L11" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="14.25" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>6</v>
       </c>
@@ -861,20 +916,24 @@
       <c r="D12" s="3">
         <v>145</v>
       </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="11">
+      <c r="E12" s="12"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="12">
         <v>105</v>
       </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="7">
+      <c r="H12" s="13"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="7">
         <v>60</v>
       </c>
-      <c r="J12" s="7">
+      <c r="K12" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L12" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>7</v>
       </c>
@@ -885,22 +944,26 @@
         <v>46265</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="11">
+      <c r="E13" s="12">
         <v>85</v>
       </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="11">
+      <c r="F13" s="13"/>
+      <c r="G13" s="12">
         <v>70</v>
       </c>
-      <c r="H13" s="12"/>
-      <c r="I13" s="7" t="s">
+      <c r="H13" s="13"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J13" s="7">
+      <c r="K13" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L13" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>8</v>
       </c>
@@ -913,20 +976,24 @@
       <c r="D14" s="3">
         <v>130</v>
       </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="11">
+      <c r="E14" s="12"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="12">
         <v>115</v>
       </c>
-      <c r="H14" s="12"/>
-      <c r="I14" s="7">
+      <c r="H14" s="13"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="7">
         <v>50</v>
       </c>
-      <c r="J14" s="7">
+      <c r="K14" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L14" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>9</v>
       </c>
@@ -939,20 +1006,24 @@
       <c r="D15" s="3">
         <v>150</v>
       </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="11">
+      <c r="E15" s="12"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="12">
         <v>130</v>
       </c>
-      <c r="H15" s="12"/>
-      <c r="I15" s="7">
+      <c r="H15" s="13"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="7">
         <v>50</v>
       </c>
-      <c r="J15" s="7">
+      <c r="K15" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L15" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>7</v>
       </c>
@@ -965,20 +1036,24 @@
       <c r="D16" s="3">
         <v>110</v>
       </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="11">
+      <c r="E16" s="12"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="12">
         <v>95</v>
       </c>
-      <c r="H16" s="12"/>
-      <c r="I16" s="7">
+      <c r="H16" s="13"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="7">
         <v>50</v>
       </c>
-      <c r="J16" s="7">
+      <c r="K16" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L16" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="14.25" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>8</v>
       </c>
@@ -991,20 +1066,24 @@
       <c r="D17" s="3">
         <v>150</v>
       </c>
-      <c r="E17" s="11"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="11">
+      <c r="E17" s="12"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="12">
         <v>130</v>
       </c>
-      <c r="H17" s="12"/>
-      <c r="I17" s="7">
+      <c r="H17" s="13"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="7">
         <v>50</v>
       </c>
-      <c r="J17" s="7">
+      <c r="K17" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L17" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="14.25" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>9</v>
       </c>
@@ -1017,20 +1096,24 @@
       <c r="D18" s="3">
         <v>130</v>
       </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="11">
+      <c r="E18" s="12"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="12">
         <v>115</v>
       </c>
-      <c r="H18" s="12"/>
-      <c r="I18" s="7">
+      <c r="H18" s="13"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="7">
         <v>50</v>
       </c>
-      <c r="J18" s="7">
+      <c r="K18" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L18" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="14.25" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>7</v>
       </c>
@@ -1045,18 +1128,22 @@
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="7"/>
-      <c r="G19" s="11">
+      <c r="G19" s="12">
         <v>95</v>
       </c>
-      <c r="H19" s="12"/>
-      <c r="I19" s="7">
+      <c r="H19" s="13"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="7">
         <v>50</v>
       </c>
-      <c r="J19" s="7">
+      <c r="K19" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L19" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="14.25" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>8</v>
       </c>
@@ -1071,18 +1158,22 @@
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="11">
+      <c r="G20" s="12">
         <v>115</v>
       </c>
-      <c r="H20" s="12"/>
-      <c r="I20" s="7">
+      <c r="H20" s="13"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="7">
         <v>50</v>
       </c>
-      <c r="J20" s="7">
+      <c r="K20" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L20" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="14.25" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>9</v>
       </c>
@@ -1097,18 +1188,22 @@
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="7"/>
-      <c r="G21" s="11">
+      <c r="G21" s="12">
         <v>130</v>
       </c>
-      <c r="H21" s="12"/>
-      <c r="I21" s="7">
+      <c r="H21" s="13"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="7">
         <v>50</v>
       </c>
-      <c r="J21" s="7">
+      <c r="K21" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L21" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="14.25" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>7</v>
       </c>
@@ -1123,18 +1218,22 @@
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="11">
+      <c r="G22" s="12">
         <v>95</v>
       </c>
-      <c r="H22" s="12"/>
-      <c r="I22" s="7">
+      <c r="H22" s="13"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="7">
         <v>50</v>
       </c>
-      <c r="J22" s="7">
+      <c r="K22" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L22" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="14.25" customHeight="1">
       <c r="A23" s="4" t="s">
         <v>10</v>
       </c>
@@ -1147,20 +1246,24 @@
       <c r="D23" s="3">
         <v>90</v>
       </c>
-      <c r="E23" s="11"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="11">
+      <c r="E23" s="12"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="12">
         <v>80</v>
       </c>
-      <c r="H23" s="12"/>
-      <c r="I23" s="7">
+      <c r="H23" s="13"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="7">
         <v>60</v>
       </c>
-      <c r="J23" s="7">
+      <c r="K23" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L23" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="14.25" customHeight="1">
       <c r="A24" s="4" t="s">
         <v>10</v>
       </c>
@@ -1173,20 +1276,24 @@
       <c r="D24" s="3">
         <v>105</v>
       </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="11">
+      <c r="E24" s="12"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="12">
         <v>90</v>
       </c>
-      <c r="H24" s="12"/>
-      <c r="I24" s="7">
+      <c r="H24" s="13"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="7">
         <v>60</v>
       </c>
-      <c r="J24" s="7">
+      <c r="K24" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L24" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="14.25" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>10</v>
       </c>
@@ -1199,20 +1306,24 @@
       <c r="D25" s="3">
         <v>160</v>
       </c>
-      <c r="E25" s="11"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="11">
+      <c r="E25" s="12"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="12">
         <v>140</v>
       </c>
-      <c r="H25" s="12"/>
-      <c r="I25" s="7">
+      <c r="H25" s="13"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="7">
         <v>60</v>
       </c>
-      <c r="J25" s="7">
+      <c r="K25" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L25" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="14.25" customHeight="1">
       <c r="A26" s="4" t="s">
         <v>10</v>
       </c>
@@ -1227,18 +1338,22 @@
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="11">
+      <c r="G26" s="12">
         <v>150</v>
       </c>
-      <c r="H26" s="12"/>
-      <c r="I26" s="7">
+      <c r="H26" s="13"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="7">
         <v>60</v>
       </c>
-      <c r="J26" s="7">
+      <c r="K26" s="7">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L26" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="14.25" customHeight="1">
       <c r="A27" s="4" t="s">
         <v>10</v>
       </c>
@@ -1253,18 +1368,22 @@
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="7"/>
-      <c r="G27" s="11">
+      <c r="G27" s="12">
         <v>90</v>
       </c>
-      <c r="H27" s="12"/>
-      <c r="I27" s="7">
+      <c r="H27" s="13"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="7">
         <v>60</v>
       </c>
-      <c r="J27" s="7">
+      <c r="K27" s="7">
         <v>12</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L27" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="14.25" customHeight="1">
       <c r="A28" s="4" t="s">
         <v>10</v>
       </c>
@@ -1279,18 +1398,22 @@
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="11">
+      <c r="G28" s="12">
         <v>150</v>
       </c>
-      <c r="H28" s="12"/>
-      <c r="I28" s="7">
+      <c r="H28" s="13"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="7">
         <v>60</v>
       </c>
-      <c r="J28" s="7">
+      <c r="K28" s="7">
         <v>12</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L28" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="14.25" customHeight="1">
       <c r="A29" s="4" t="s">
         <v>10</v>
       </c>
@@ -1305,18 +1428,22 @@
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="7"/>
-      <c r="G29" s="11">
+      <c r="G29" s="12">
         <v>90</v>
       </c>
-      <c r="H29" s="12"/>
-      <c r="I29" s="7">
+      <c r="H29" s="13"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="7">
         <v>60</v>
       </c>
-      <c r="J29" s="7">
+      <c r="K29" s="7">
         <v>12</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L29" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="14.25" customHeight="1">
       <c r="A30" s="4" t="s">
         <v>10</v>
       </c>
@@ -1331,18 +1458,22 @@
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="11">
+      <c r="G30" s="12">
         <v>80</v>
       </c>
-      <c r="H30" s="12"/>
-      <c r="I30" s="7">
+      <c r="H30" s="13"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="7">
         <v>60</v>
       </c>
-      <c r="J30" s="7">
+      <c r="K30" s="7">
         <v>12</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L30" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="14.25" customHeight="1">
       <c r="A31" s="4" t="s">
         <v>10</v>
       </c>
@@ -1357,18 +1488,22 @@
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="11">
+      <c r="G31" s="12">
         <v>90</v>
       </c>
-      <c r="H31" s="12"/>
-      <c r="I31" s="7">
+      <c r="H31" s="13"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="7">
         <v>60</v>
       </c>
-      <c r="J31" s="7">
+      <c r="K31" s="7">
         <v>12</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L31" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="14.25" customHeight="1">
       <c r="A32" s="4" t="s">
         <v>10</v>
       </c>
@@ -1383,18 +1518,22 @@
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="11">
+      <c r="G32" s="12">
         <v>150</v>
       </c>
-      <c r="H32" s="12"/>
-      <c r="I32" s="7">
+      <c r="H32" s="13"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="7">
         <v>60</v>
       </c>
-      <c r="J32" s="7">
+      <c r="K32" s="7">
         <v>12</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L32" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="14.25" customHeight="1">
       <c r="A33" s="4" t="s">
         <v>11</v>
       </c>
@@ -1405,22 +1544,26 @@
         <v>46234</v>
       </c>
       <c r="D33" s="3"/>
-      <c r="E33" s="11">
+      <c r="E33" s="12">
         <v>84</v>
       </c>
-      <c r="F33" s="12"/>
-      <c r="G33" s="11">
+      <c r="F33" s="13"/>
+      <c r="G33" s="12">
         <v>69</v>
       </c>
-      <c r="H33" s="12"/>
-      <c r="I33" s="7" t="s">
+      <c r="H33" s="13"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J33" s="7">
+      <c r="K33" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L33" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="14.25" customHeight="1">
       <c r="A34" s="4" t="s">
         <v>12</v>
       </c>
@@ -1431,22 +1574,26 @@
         <v>46276</v>
       </c>
       <c r="D34" s="3"/>
-      <c r="E34" s="11">
+      <c r="E34" s="12">
         <v>80</v>
       </c>
-      <c r="F34" s="12"/>
-      <c r="G34" s="11">
+      <c r="F34" s="13"/>
+      <c r="G34" s="12">
         <v>80</v>
       </c>
-      <c r="H34" s="12"/>
-      <c r="I34" s="7">
+      <c r="H34" s="13"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="7">
         <v>45</v>
       </c>
-      <c r="J34" s="7">
+      <c r="K34" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L34" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="14.25" customHeight="1">
       <c r="A35" s="4" t="s">
         <v>11</v>
       </c>
@@ -1457,22 +1604,26 @@
         <v>46295</v>
       </c>
       <c r="D35" s="3"/>
-      <c r="E35" s="11">
+      <c r="E35" s="12">
         <v>90</v>
       </c>
-      <c r="F35" s="12"/>
-      <c r="G35" s="11">
+      <c r="F35" s="13"/>
+      <c r="G35" s="12">
         <v>90</v>
       </c>
-      <c r="H35" s="12"/>
-      <c r="I35" s="7">
+      <c r="H35" s="13"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="7">
         <v>45</v>
       </c>
-      <c r="J35" s="7">
+      <c r="K35" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L35" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="14.25" customHeight="1">
       <c r="A36" s="4" t="s">
         <v>12</v>
       </c>
@@ -1485,20 +1636,24 @@
       <c r="D36" s="3">
         <v>122</v>
       </c>
-      <c r="E36" s="11"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="11">
+      <c r="E36" s="12"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="12">
         <v>102</v>
       </c>
-      <c r="H36" s="12"/>
-      <c r="I36" s="7">
+      <c r="H36" s="13"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="7">
         <v>45</v>
       </c>
-      <c r="J36" s="7">
+      <c r="K36" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L36" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="14.25" customHeight="1">
       <c r="A37" s="4" t="s">
         <v>11</v>
       </c>
@@ -1511,20 +1666,24 @@
       <c r="D37" s="3">
         <v>86</v>
       </c>
-      <c r="E37" s="11"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="11">
+      <c r="E37" s="12"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="12">
         <v>66</v>
       </c>
-      <c r="H37" s="12"/>
-      <c r="I37" s="7">
+      <c r="H37" s="13"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="7">
         <v>45</v>
       </c>
-      <c r="J37" s="7">
+      <c r="K37" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L37" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="14.25" customHeight="1">
       <c r="A38" s="4" t="s">
         <v>12</v>
       </c>
@@ -1537,20 +1696,24 @@
       <c r="D38" s="3">
         <v>86</v>
       </c>
-      <c r="E38" s="11"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="11">
+      <c r="E38" s="12"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="12">
         <v>66</v>
       </c>
-      <c r="H38" s="12"/>
-      <c r="I38" s="7">
+      <c r="H38" s="13"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="7">
         <v>45</v>
       </c>
-      <c r="J38" s="7">
+      <c r="K38" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L38" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="14.25" customHeight="1">
       <c r="A39" s="4" t="s">
         <v>11</v>
       </c>
@@ -1563,20 +1726,24 @@
       <c r="D39" s="3">
         <v>104</v>
       </c>
-      <c r="E39" s="11"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="11">
+      <c r="E39" s="12"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="12">
         <v>84</v>
       </c>
-      <c r="H39" s="12"/>
-      <c r="I39" s="7">
+      <c r="H39" s="13"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="7">
         <v>45</v>
       </c>
-      <c r="J39" s="7">
+      <c r="K39" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L39" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="14.25" customHeight="1">
       <c r="A40" s="4" t="s">
         <v>12</v>
       </c>
@@ -1589,20 +1756,24 @@
       <c r="D40" s="3">
         <v>122</v>
       </c>
-      <c r="E40" s="11"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="11">
+      <c r="E40" s="12"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="12">
         <v>102</v>
       </c>
-      <c r="H40" s="12"/>
-      <c r="I40" s="7">
+      <c r="H40" s="13"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="7">
         <v>45</v>
       </c>
-      <c r="J40" s="7">
+      <c r="K40" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L40" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="14.25" customHeight="1">
       <c r="A41" s="4" t="s">
         <v>11</v>
       </c>
@@ -1615,20 +1786,24 @@
       <c r="D41" s="3">
         <v>104</v>
       </c>
-      <c r="E41" s="11"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="11">
+      <c r="E41" s="12"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="12">
         <v>84</v>
       </c>
-      <c r="H41" s="12"/>
-      <c r="I41" s="7">
+      <c r="H41" s="13"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="7">
         <v>45</v>
       </c>
-      <c r="J41" s="7">
+      <c r="K41" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L41" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="14.25" customHeight="1">
       <c r="A42" s="4" t="s">
         <v>12</v>
       </c>
@@ -1641,20 +1816,24 @@
       <c r="D42" s="3">
         <v>86</v>
       </c>
-      <c r="E42" s="11"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="11">
+      <c r="E42" s="12"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="12">
         <v>66</v>
       </c>
-      <c r="H42" s="12"/>
-      <c r="I42" s="7">
+      <c r="H42" s="13"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="7">
         <v>45</v>
       </c>
-      <c r="J42" s="7">
+      <c r="K42" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L42" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="14.25" customHeight="1">
       <c r="A43" s="4" t="s">
         <v>11</v>
       </c>
@@ -1667,20 +1846,24 @@
       <c r="D43" s="3">
         <v>104</v>
       </c>
-      <c r="E43" s="11"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="11">
+      <c r="E43" s="12"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="12">
         <v>84</v>
       </c>
-      <c r="H43" s="12"/>
-      <c r="I43" s="7">
+      <c r="H43" s="13"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="7">
         <v>45</v>
       </c>
-      <c r="J43" s="7">
+      <c r="K43" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L43" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="14.25" customHeight="1">
       <c r="A44" s="4" t="s">
         <v>12</v>
       </c>
@@ -1693,20 +1876,24 @@
       <c r="D44" s="3">
         <v>122</v>
       </c>
-      <c r="E44" s="11"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="11">
+      <c r="E44" s="12"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="12">
         <v>102</v>
       </c>
-      <c r="H44" s="12"/>
-      <c r="I44" s="7">
+      <c r="H44" s="13"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="7">
         <v>45</v>
       </c>
-      <c r="J44" s="7">
+      <c r="K44" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L44" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="14.25" customHeight="1">
       <c r="A45" s="4" t="s">
         <v>11</v>
       </c>
@@ -1719,20 +1906,24 @@
       <c r="D45" s="3">
         <v>86</v>
       </c>
-      <c r="E45" s="11"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="11">
+      <c r="E45" s="12"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="12">
         <v>66</v>
       </c>
-      <c r="H45" s="12"/>
-      <c r="I45" s="7">
+      <c r="H45" s="13"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="7">
         <v>45</v>
       </c>
-      <c r="J45" s="7">
+      <c r="K45" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L45" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="14.25" customHeight="1">
       <c r="A46" s="4" t="s">
         <v>13</v>
       </c>
@@ -1743,20 +1934,24 @@
         <v>46234</v>
       </c>
       <c r="D46" s="3"/>
-      <c r="E46" s="11">
+      <c r="E46" s="12">
         <v>60</v>
       </c>
-      <c r="F46" s="12"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="7" t="s">
-        <v>27</v>
-      </c>
+      <c r="F46" s="13"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="10"/>
       <c r="J46" s="7" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" ht="14.25" customHeight="1">
+      <c r="K46" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L46" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="14.25" customHeight="1">
       <c r="A47" s="4" t="s">
         <v>13</v>
       </c>
@@ -1769,20 +1964,24 @@
       <c r="D47" s="3">
         <v>70</v>
       </c>
-      <c r="E47" s="11"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="11">
+      <c r="E47" s="12"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="12">
         <v>70</v>
       </c>
-      <c r="H47" s="12"/>
-      <c r="I47" s="7">
+      <c r="H47" s="13"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="7">
         <v>50</v>
       </c>
-      <c r="J47" s="7">
+      <c r="K47" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L47" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="14.25" customHeight="1">
       <c r="A48" s="4" t="s">
         <v>13</v>
       </c>
@@ -1795,20 +1994,24 @@
       <c r="D48" s="3">
         <v>90</v>
       </c>
-      <c r="E48" s="11"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="11">
+      <c r="E48" s="12"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="12">
         <v>90</v>
       </c>
-      <c r="H48" s="12"/>
-      <c r="I48" s="7">
+      <c r="H48" s="13"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="7">
         <v>70</v>
       </c>
-      <c r="J48" s="7">
+      <c r="K48" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L48" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="14.25" customHeight="1">
       <c r="A49" s="4" t="s">
         <v>13</v>
       </c>
@@ -1821,20 +2024,24 @@
       <c r="D49" s="3">
         <v>160</v>
       </c>
-      <c r="E49" s="11"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="11">
+      <c r="E49" s="12"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="12">
         <v>160</v>
       </c>
-      <c r="H49" s="12"/>
-      <c r="I49" s="7">
+      <c r="H49" s="13"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="7">
         <v>70</v>
       </c>
-      <c r="J49" s="7">
+      <c r="K49" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L49" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="14.25" customHeight="1">
       <c r="A50" s="4" t="s">
         <v>13</v>
       </c>
@@ -1847,20 +2054,24 @@
       <c r="D50" s="3">
         <v>100</v>
       </c>
-      <c r="E50" s="11"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="11">
+      <c r="E50" s="12"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="12">
         <v>100</v>
       </c>
-      <c r="H50" s="12"/>
-      <c r="I50" s="7">
+      <c r="H50" s="13"/>
+      <c r="I50" s="10"/>
+      <c r="J50" s="7">
         <v>50</v>
       </c>
-      <c r="J50" s="7">
+      <c r="K50" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L50" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="14.25" customHeight="1">
       <c r="A51" s="4" t="s">
         <v>13</v>
       </c>
@@ -1875,18 +2086,22 @@
       </c>
       <c r="E51" s="6"/>
       <c r="F51" s="7"/>
-      <c r="G51" s="11">
+      <c r="G51" s="12">
         <v>100</v>
       </c>
-      <c r="H51" s="12"/>
-      <c r="I51" s="7">
+      <c r="H51" s="13"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="7">
         <v>70</v>
       </c>
-      <c r="J51" s="7">
+      <c r="K51" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L51" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="14.25" customHeight="1">
       <c r="A52" s="4" t="s">
         <v>13</v>
       </c>
@@ -1901,18 +2116,22 @@
       </c>
       <c r="E52" s="6"/>
       <c r="F52" s="7"/>
-      <c r="G52" s="11">
+      <c r="G52" s="12">
         <v>160</v>
       </c>
-      <c r="H52" s="12"/>
-      <c r="I52" s="7">
+      <c r="H52" s="13"/>
+      <c r="I52" s="10"/>
+      <c r="J52" s="7">
         <v>70</v>
       </c>
-      <c r="J52" s="7">
+      <c r="K52" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L52" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="14.25" customHeight="1">
       <c r="A53" s="4" t="s">
         <v>13</v>
       </c>
@@ -1925,20 +2144,24 @@
       <c r="D53" s="3">
         <v>80</v>
       </c>
-      <c r="E53" s="11"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="11">
+      <c r="E53" s="12"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="12">
         <v>80</v>
       </c>
-      <c r="H53" s="12"/>
-      <c r="I53" s="7" t="s">
-        <v>27</v>
-      </c>
+      <c r="H53" s="13"/>
+      <c r="I53" s="10"/>
       <c r="J53" s="7" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" ht="14.25" customHeight="1">
+      <c r="K53" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L53" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="14.25" customHeight="1">
       <c r="A54" s="4" t="s">
         <v>14</v>
       </c>
@@ -1951,20 +2174,24 @@
       <c r="D54" s="3">
         <v>55</v>
       </c>
-      <c r="E54" s="11"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="11">
+      <c r="E54" s="12"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="12">
         <v>55</v>
       </c>
-      <c r="H54" s="12"/>
-      <c r="I54" s="7" t="s">
+      <c r="H54" s="13"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J54" s="7">
+      <c r="K54" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L54" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="14.25" customHeight="1">
       <c r="A55" s="4" t="s">
         <v>15</v>
       </c>
@@ -1977,20 +2204,24 @@
       <c r="D55" s="3">
         <v>75</v>
       </c>
-      <c r="E55" s="11"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="11">
+      <c r="E55" s="12"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="12">
         <v>75</v>
       </c>
-      <c r="H55" s="12"/>
-      <c r="I55" s="7" t="s">
+      <c r="H55" s="13"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J55" s="7">
+      <c r="K55" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L55" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="14.25" customHeight="1">
       <c r="A56" s="4" t="s">
         <v>14</v>
       </c>
@@ -2003,20 +2234,24 @@
       <c r="D56" s="3">
         <v>130</v>
       </c>
-      <c r="E56" s="11"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="11">
+      <c r="E56" s="12"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="12">
         <v>130</v>
       </c>
-      <c r="H56" s="12"/>
-      <c r="I56" s="7">
+      <c r="H56" s="13"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="7">
         <v>55</v>
       </c>
-      <c r="J56" s="7">
+      <c r="K56" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L56" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="14.25" customHeight="1">
       <c r="A57" s="4" t="s">
         <v>15</v>
       </c>
@@ -2029,20 +2264,24 @@
       <c r="D57" s="3">
         <v>160</v>
       </c>
-      <c r="E57" s="11"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="11">
+      <c r="E57" s="12"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="12">
         <v>160</v>
       </c>
-      <c r="H57" s="12"/>
-      <c r="I57" s="7">
+      <c r="H57" s="13"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="7">
         <v>55</v>
       </c>
-      <c r="J57" s="7">
+      <c r="K57" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L57" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="14.25" customHeight="1">
       <c r="A58" s="4" t="s">
         <v>14</v>
       </c>
@@ -2055,20 +2294,24 @@
       <c r="D58" s="3">
         <v>65</v>
       </c>
-      <c r="E58" s="11"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="11">
+      <c r="E58" s="12"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="12">
         <v>65</v>
       </c>
-      <c r="H58" s="12"/>
-      <c r="I58" s="7">
+      <c r="H58" s="13"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="7">
         <v>55</v>
       </c>
-      <c r="J58" s="7">
+      <c r="K58" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L58" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="14.25" customHeight="1">
       <c r="A59" s="4" t="s">
         <v>15</v>
       </c>
@@ -2081,20 +2324,24 @@
       <c r="D59" s="3">
         <v>80</v>
       </c>
-      <c r="E59" s="11"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="11">
+      <c r="E59" s="12"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="12">
         <v>80</v>
       </c>
-      <c r="H59" s="12"/>
-      <c r="I59" s="7">
+      <c r="H59" s="13"/>
+      <c r="I59" s="10"/>
+      <c r="J59" s="7">
         <v>55</v>
       </c>
-      <c r="J59" s="7">
+      <c r="K59" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L59" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="14.25" customHeight="1">
       <c r="A60" s="4" t="s">
         <v>14</v>
       </c>
@@ -2107,20 +2354,24 @@
       <c r="D60" s="3">
         <v>130</v>
       </c>
-      <c r="E60" s="11"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="11">
+      <c r="E60" s="12"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="12">
         <v>130</v>
       </c>
-      <c r="H60" s="12"/>
-      <c r="I60" s="7">
+      <c r="H60" s="13"/>
+      <c r="I60" s="10"/>
+      <c r="J60" s="7">
         <v>55</v>
       </c>
-      <c r="J60" s="7">
+      <c r="K60" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L60" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="14.25" customHeight="1">
       <c r="A61" s="4" t="s">
         <v>15</v>
       </c>
@@ -2133,20 +2384,24 @@
       <c r="D61" s="3">
         <v>160</v>
       </c>
-      <c r="E61" s="11"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="11">
+      <c r="E61" s="12"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="12">
         <v>160</v>
       </c>
-      <c r="H61" s="12"/>
-      <c r="I61" s="7">
+      <c r="H61" s="13"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="7">
         <v>55</v>
       </c>
-      <c r="J61" s="7">
+      <c r="K61" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L61" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="14.25" customHeight="1">
       <c r="A62" s="4" t="s">
         <v>14</v>
       </c>
@@ -2159,20 +2414,24 @@
       <c r="D62" s="3">
         <v>65</v>
       </c>
-      <c r="E62" s="11"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="11">
+      <c r="E62" s="12"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="12">
         <v>65</v>
       </c>
-      <c r="H62" s="12"/>
-      <c r="I62" s="7">
+      <c r="H62" s="13"/>
+      <c r="I62" s="10"/>
+      <c r="J62" s="7">
         <v>55</v>
       </c>
-      <c r="J62" s="7">
+      <c r="K62" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L62" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="14.25" customHeight="1">
       <c r="A63" s="4" t="s">
         <v>15</v>
       </c>
@@ -2185,20 +2444,24 @@
       <c r="D63" s="3">
         <v>80</v>
       </c>
-      <c r="E63" s="11"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="11">
+      <c r="E63" s="12"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="12">
         <v>80</v>
       </c>
-      <c r="H63" s="12"/>
-      <c r="I63" s="7">
+      <c r="H63" s="13"/>
+      <c r="I63" s="10"/>
+      <c r="J63" s="7">
         <v>55</v>
       </c>
-      <c r="J63" s="7">
+      <c r="K63" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L63" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="14.25" customHeight="1">
       <c r="A64" s="4" t="s">
         <v>16</v>
       </c>
@@ -2211,20 +2474,24 @@
       <c r="D64" s="3">
         <v>84</v>
       </c>
-      <c r="E64" s="11"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="11">
+      <c r="E64" s="12"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="12">
         <v>70</v>
       </c>
-      <c r="H64" s="12"/>
-      <c r="I64" s="7">
+      <c r="H64" s="13"/>
+      <c r="I64" s="10"/>
+      <c r="J64" s="7">
         <v>50</v>
       </c>
-      <c r="J64" s="7">
+      <c r="K64" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L64" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="14.25" customHeight="1">
       <c r="A65" s="4" t="s">
         <v>17</v>
       </c>
@@ -2237,20 +2504,24 @@
       <c r="D65" s="3">
         <v>128</v>
       </c>
-      <c r="E65" s="11"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="11">
+      <c r="E65" s="12"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="12">
         <v>95</v>
       </c>
-      <c r="H65" s="12"/>
-      <c r="I65" s="7">
+      <c r="H65" s="13"/>
+      <c r="I65" s="10"/>
+      <c r="J65" s="7">
         <v>50</v>
       </c>
-      <c r="J65" s="7">
+      <c r="K65" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L65" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="14.25" customHeight="1">
       <c r="A66" s="4" t="s">
         <v>18</v>
       </c>
@@ -2263,20 +2534,24 @@
       <c r="D66" s="3">
         <v>144</v>
       </c>
-      <c r="E66" s="11"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="11">
+      <c r="E66" s="12"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="12">
         <v>110</v>
       </c>
-      <c r="H66" s="12"/>
-      <c r="I66" s="7">
+      <c r="H66" s="13"/>
+      <c r="I66" s="10"/>
+      <c r="J66" s="7">
         <v>50</v>
       </c>
-      <c r="J66" s="7">
+      <c r="K66" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L66" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="14.25" customHeight="1">
       <c r="A67" s="4" t="s">
         <v>16</v>
       </c>
@@ -2289,20 +2564,24 @@
       <c r="D67" s="3">
         <v>144</v>
       </c>
-      <c r="E67" s="11"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="11">
+      <c r="E67" s="12"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="12">
         <v>110</v>
       </c>
-      <c r="H67" s="12"/>
-      <c r="I67" s="7">
+      <c r="H67" s="13"/>
+      <c r="I67" s="10"/>
+      <c r="J67" s="7">
         <v>50</v>
       </c>
-      <c r="J67" s="7">
+      <c r="K67" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L67" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="14.25" customHeight="1">
       <c r="A68" s="4" t="s">
         <v>17</v>
       </c>
@@ -2315,20 +2594,24 @@
       <c r="D68" s="3">
         <v>95</v>
       </c>
-      <c r="E68" s="11"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="11">
+      <c r="E68" s="12"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="12">
         <v>70</v>
       </c>
-      <c r="H68" s="12"/>
-      <c r="I68" s="7">
+      <c r="H68" s="13"/>
+      <c r="I68" s="10"/>
+      <c r="J68" s="7">
         <v>50</v>
       </c>
-      <c r="J68" s="7">
+      <c r="K68" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L68" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="14.25" customHeight="1">
       <c r="A69" s="4" t="s">
         <v>16</v>
       </c>
@@ -2341,20 +2624,24 @@
       <c r="D69" s="3">
         <v>144</v>
       </c>
-      <c r="E69" s="11"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="11">
+      <c r="E69" s="12"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="12">
         <v>95</v>
       </c>
-      <c r="H69" s="12"/>
-      <c r="I69" s="7">
+      <c r="H69" s="13"/>
+      <c r="I69" s="10"/>
+      <c r="J69" s="7">
         <v>50</v>
       </c>
-      <c r="J69" s="7">
+      <c r="K69" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L69" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="14.25" customHeight="1">
       <c r="A70" s="4" t="s">
         <v>17</v>
       </c>
@@ -2367,20 +2654,24 @@
       <c r="D70" s="3">
         <v>95</v>
       </c>
-      <c r="E70" s="11"/>
-      <c r="F70" s="12"/>
-      <c r="G70" s="11">
+      <c r="E70" s="12"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="12">
         <v>70</v>
       </c>
-      <c r="H70" s="12"/>
-      <c r="I70" s="7">
+      <c r="H70" s="13"/>
+      <c r="I70" s="10"/>
+      <c r="J70" s="7">
         <v>50</v>
       </c>
-      <c r="J70" s="7">
+      <c r="K70" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L70" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="14.25" customHeight="1">
       <c r="A71" s="4" t="s">
         <v>18</v>
       </c>
@@ -2393,20 +2684,24 @@
       <c r="D71" s="3">
         <v>144</v>
       </c>
-      <c r="E71" s="11"/>
-      <c r="F71" s="12"/>
-      <c r="G71" s="11">
+      <c r="E71" s="12"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="12">
         <v>95</v>
       </c>
-      <c r="H71" s="12"/>
-      <c r="I71" s="7">
+      <c r="H71" s="13"/>
+      <c r="I71" s="10"/>
+      <c r="J71" s="7">
         <v>50</v>
       </c>
-      <c r="J71" s="7">
+      <c r="K71" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L71" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="14.25" customHeight="1">
       <c r="A72" s="4" t="s">
         <v>16</v>
       </c>
@@ -2419,20 +2714,24 @@
       <c r="D72" s="3">
         <v>144</v>
       </c>
-      <c r="E72" s="11"/>
-      <c r="F72" s="12"/>
-      <c r="G72" s="11">
+      <c r="E72" s="12"/>
+      <c r="F72" s="13"/>
+      <c r="G72" s="12">
         <v>110</v>
       </c>
-      <c r="H72" s="12"/>
-      <c r="I72" s="7">
+      <c r="H72" s="13"/>
+      <c r="I72" s="10"/>
+      <c r="J72" s="7">
         <v>50</v>
       </c>
-      <c r="J72" s="7">
+      <c r="K72" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L72" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="14.25" customHeight="1">
       <c r="A73" s="4" t="s">
         <v>19</v>
       </c>
@@ -2445,20 +2744,24 @@
       <c r="D73" s="3">
         <v>80</v>
       </c>
-      <c r="E73" s="11"/>
-      <c r="F73" s="12"/>
-      <c r="G73" s="11">
+      <c r="E73" s="12"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="12">
         <v>80</v>
       </c>
-      <c r="H73" s="12"/>
-      <c r="I73" s="7" t="s">
+      <c r="H73" s="13"/>
+      <c r="I73" s="10"/>
+      <c r="J73" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J73" s="7" t="s">
+      <c r="K73" s="7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L73" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="14.25" customHeight="1">
       <c r="A74" s="4" t="s">
         <v>20</v>
       </c>
@@ -2471,20 +2774,24 @@
       <c r="D74" s="3">
         <v>110</v>
       </c>
-      <c r="E74" s="11"/>
-      <c r="F74" s="12"/>
-      <c r="G74" s="11">
+      <c r="E74" s="12"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="12">
         <v>110</v>
       </c>
-      <c r="H74" s="12"/>
-      <c r="I74" s="7" t="s">
+      <c r="H74" s="13"/>
+      <c r="I74" s="10"/>
+      <c r="J74" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J74" s="7" t="s">
+      <c r="K74" s="7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L74" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="14.25" customHeight="1">
       <c r="A75" s="4" t="s">
         <v>19</v>
       </c>
@@ -2497,20 +2804,24 @@
       <c r="D75" s="3">
         <v>130</v>
       </c>
-      <c r="E75" s="11"/>
-      <c r="F75" s="12"/>
-      <c r="G75" s="11">
+      <c r="E75" s="12"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="12">
         <v>130</v>
       </c>
-      <c r="H75" s="12"/>
-      <c r="I75" s="7" t="s">
+      <c r="H75" s="13"/>
+      <c r="I75" s="10"/>
+      <c r="J75" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J75" s="7" t="s">
+      <c r="K75" s="7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L75" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="14.25" customHeight="1">
       <c r="A76" s="4" t="s">
         <v>20</v>
       </c>
@@ -2523,22 +2834,26 @@
       <c r="D76" s="3">
         <v>190</v>
       </c>
-      <c r="E76" s="11" t="s">
+      <c r="E76" s="12"/>
+      <c r="F76" s="13"/>
+      <c r="G76" s="12">
+        <v>190</v>
+      </c>
+      <c r="H76" s="13"/>
+      <c r="I76" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F76" s="12"/>
-      <c r="G76" s="11">
-        <v>190</v>
-      </c>
-      <c r="H76" s="12"/>
-      <c r="I76" s="7" t="s">
+      <c r="J76" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J76" s="7" t="s">
+      <c r="K76" s="7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L76" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="14.25" customHeight="1">
       <c r="A77" s="4" t="s">
         <v>19</v>
       </c>
@@ -2551,22 +2866,26 @@
       <c r="D77" s="3">
         <v>120</v>
       </c>
-      <c r="E77" s="11" t="s">
+      <c r="E77" s="12"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="12">
+        <v>120</v>
+      </c>
+      <c r="H77" s="13"/>
+      <c r="I77" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F77" s="12"/>
-      <c r="G77" s="11">
-        <v>120</v>
-      </c>
-      <c r="H77" s="12"/>
-      <c r="I77" s="7" t="s">
+      <c r="J77" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J77" s="7" t="s">
+      <c r="K77" s="7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L77" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="14.25" customHeight="1">
       <c r="A78" s="4" t="s">
         <v>20</v>
       </c>
@@ -2579,22 +2898,26 @@
       <c r="D78" s="3">
         <v>190</v>
       </c>
-      <c r="E78" s="11" t="s">
+      <c r="E78" s="12"/>
+      <c r="F78" s="13"/>
+      <c r="G78" s="12">
+        <v>190</v>
+      </c>
+      <c r="H78" s="13"/>
+      <c r="I78" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F78" s="12"/>
-      <c r="G78" s="11">
-        <v>190</v>
-      </c>
-      <c r="H78" s="12"/>
-      <c r="I78" s="7" t="s">
+      <c r="J78" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J78" s="7" t="s">
+      <c r="K78" s="7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L78" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="14.25" customHeight="1">
       <c r="A79" s="4" t="s">
         <v>19</v>
       </c>
@@ -2607,22 +2930,26 @@
       <c r="D79" s="3">
         <v>145</v>
       </c>
-      <c r="E79" s="11" t="s">
+      <c r="E79" s="12"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="12">
+        <v>145</v>
+      </c>
+      <c r="H79" s="13"/>
+      <c r="I79" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F79" s="12"/>
-      <c r="G79" s="11">
-        <v>145</v>
-      </c>
-      <c r="H79" s="12"/>
-      <c r="I79" s="7" t="s">
+      <c r="J79" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J79" s="7" t="s">
+      <c r="K79" s="7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L79" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="14.25" customHeight="1">
       <c r="A80" s="4" t="s">
         <v>20</v>
       </c>
@@ -2635,22 +2962,26 @@
       <c r="D80" s="3">
         <v>120</v>
       </c>
-      <c r="E80" s="11" t="s">
+      <c r="E80" s="12"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="12">
+        <v>120</v>
+      </c>
+      <c r="H80" s="13"/>
+      <c r="I80" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F80" s="12"/>
-      <c r="G80" s="11">
-        <v>120</v>
-      </c>
-      <c r="H80" s="12"/>
-      <c r="I80" s="7" t="s">
+      <c r="J80" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J80" s="7" t="s">
+      <c r="K80" s="7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L80" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="14.25" customHeight="1">
       <c r="A81" s="4" t="s">
         <v>21</v>
       </c>
@@ -2663,20 +2994,24 @@
       <c r="D81" s="3">
         <v>145</v>
       </c>
-      <c r="E81" s="11"/>
-      <c r="F81" s="12"/>
-      <c r="G81" s="11">
+      <c r="E81" s="12"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="12">
         <v>130</v>
       </c>
-      <c r="H81" s="12"/>
-      <c r="I81" s="7">
+      <c r="H81" s="13"/>
+      <c r="I81" s="10"/>
+      <c r="J81" s="7">
         <v>60</v>
       </c>
-      <c r="J81" s="7">
+      <c r="K81" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L81" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="14.25" customHeight="1">
       <c r="A82" s="4" t="s">
         <v>21</v>
       </c>
@@ -2689,20 +3024,24 @@
       <c r="D82" s="3">
         <v>150</v>
       </c>
-      <c r="E82" s="11"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="11">
+      <c r="E82" s="12"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="12">
         <v>135</v>
       </c>
-      <c r="H82" s="12"/>
-      <c r="I82" s="7">
+      <c r="H82" s="13"/>
+      <c r="I82" s="10"/>
+      <c r="J82" s="7">
         <v>60</v>
       </c>
-      <c r="J82" s="7">
+      <c r="K82" s="7">
         <v>12</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L82" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="14.25" customHeight="1">
       <c r="A83" s="4" t="s">
         <v>21</v>
       </c>
@@ -2715,20 +3054,24 @@
       <c r="D83" s="3">
         <v>80</v>
       </c>
-      <c r="E83" s="11"/>
-      <c r="F83" s="12"/>
-      <c r="G83" s="11">
+      <c r="E83" s="12"/>
+      <c r="F83" s="13"/>
+      <c r="G83" s="12">
         <v>70</v>
       </c>
-      <c r="H83" s="12"/>
-      <c r="I83" s="7">
+      <c r="H83" s="13"/>
+      <c r="I83" s="10"/>
+      <c r="J83" s="7">
         <v>60</v>
       </c>
-      <c r="J83" s="7">
+      <c r="K83" s="7">
         <v>12</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L83" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="14.25" customHeight="1">
       <c r="A84" s="4" t="s">
         <v>21</v>
       </c>
@@ -2739,20 +3082,24 @@
         <v>46428</v>
       </c>
       <c r="D84" s="3"/>
-      <c r="E84" s="11">
+      <c r="E84" s="12">
         <v>70</v>
       </c>
-      <c r="F84" s="12"/>
+      <c r="F84" s="13"/>
       <c r="G84" s="6"/>
       <c r="H84" s="7"/>
-      <c r="I84" s="7">
+      <c r="I84" s="10"/>
+      <c r="J84" s="7">
         <v>60</v>
       </c>
-      <c r="J84" s="7">
+      <c r="K84" s="7">
         <v>12</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L84" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="14.25" customHeight="1">
       <c r="A85" s="4" t="s">
         <v>21</v>
       </c>
@@ -2765,20 +3112,24 @@
       <c r="D85" s="3">
         <v>150</v>
       </c>
-      <c r="E85" s="11"/>
-      <c r="F85" s="12"/>
-      <c r="G85" s="11">
+      <c r="E85" s="12"/>
+      <c r="F85" s="13"/>
+      <c r="G85" s="12">
         <v>135</v>
       </c>
-      <c r="H85" s="12"/>
-      <c r="I85" s="7">
+      <c r="H85" s="13"/>
+      <c r="I85" s="10"/>
+      <c r="J85" s="7">
         <v>60</v>
       </c>
-      <c r="J85" s="7">
+      <c r="K85" s="7">
         <v>12</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L85" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="14.25" customHeight="1">
       <c r="A86" s="4" t="s">
         <v>21</v>
       </c>
@@ -2791,20 +3142,24 @@
       <c r="D86" s="3">
         <v>80</v>
       </c>
-      <c r="E86" s="11"/>
-      <c r="F86" s="12"/>
-      <c r="G86" s="11">
+      <c r="E86" s="12"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="12">
         <v>70</v>
       </c>
-      <c r="H86" s="12"/>
-      <c r="I86" s="7">
+      <c r="H86" s="13"/>
+      <c r="I86" s="10"/>
+      <c r="J86" s="7">
         <v>60</v>
       </c>
-      <c r="J86" s="7">
+      <c r="K86" s="7">
         <v>12</v>
       </c>
-    </row>
-    <row r="87" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L86" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="14.25" customHeight="1">
       <c r="A87" s="4" t="s">
         <v>21</v>
       </c>
@@ -2817,20 +3172,24 @@
       <c r="D87" s="3">
         <v>70</v>
       </c>
-      <c r="E87" s="11"/>
-      <c r="F87" s="12"/>
-      <c r="G87" s="11">
+      <c r="E87" s="12"/>
+      <c r="F87" s="13"/>
+      <c r="G87" s="12">
         <v>60</v>
       </c>
-      <c r="H87" s="12"/>
-      <c r="I87" s="7">
+      <c r="H87" s="13"/>
+      <c r="I87" s="10"/>
+      <c r="J87" s="7">
         <v>60</v>
       </c>
-      <c r="J87" s="7">
+      <c r="K87" s="7">
         <v>12</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L87" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="14.25" customHeight="1">
       <c r="A88" s="4" t="s">
         <v>21</v>
       </c>
@@ -2843,20 +3202,24 @@
       <c r="D88" s="3">
         <v>80</v>
       </c>
-      <c r="E88" s="11"/>
-      <c r="F88" s="12"/>
-      <c r="G88" s="11">
+      <c r="E88" s="12"/>
+      <c r="F88" s="13"/>
+      <c r="G88" s="12">
         <v>70</v>
       </c>
-      <c r="H88" s="12"/>
-      <c r="I88" s="7">
+      <c r="H88" s="13"/>
+      <c r="I88" s="10"/>
+      <c r="J88" s="7">
         <v>60</v>
       </c>
-      <c r="J88" s="7">
+      <c r="K88" s="7">
         <v>12</v>
       </c>
-    </row>
-    <row r="89" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L88" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="14.25" customHeight="1">
       <c r="A89" s="4" t="s">
         <v>22</v>
       </c>
@@ -2867,20 +3230,24 @@
         <v>46234</v>
       </c>
       <c r="D89" s="3"/>
-      <c r="E89" s="11">
+      <c r="E89" s="12">
         <v>50</v>
       </c>
-      <c r="F89" s="12"/>
-      <c r="G89" s="11"/>
-      <c r="H89" s="12"/>
-      <c r="I89" s="7" t="s">
+      <c r="F89" s="13"/>
+      <c r="G89" s="12"/>
+      <c r="H89" s="13"/>
+      <c r="I89" s="10"/>
+      <c r="J89" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J89" s="7">
+      <c r="K89" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L89" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="14.25" customHeight="1">
       <c r="A90" s="4" t="s">
         <v>22</v>
       </c>
@@ -2893,20 +3260,24 @@
       <c r="D90" s="3">
         <v>60</v>
       </c>
-      <c r="E90" s="11"/>
-      <c r="F90" s="12"/>
-      <c r="G90" s="11">
+      <c r="E90" s="12"/>
+      <c r="F90" s="13"/>
+      <c r="G90" s="12">
         <v>60</v>
       </c>
-      <c r="H90" s="12"/>
-      <c r="I90" s="7">
+      <c r="H90" s="13"/>
+      <c r="I90" s="10"/>
+      <c r="J90" s="7">
         <v>50</v>
       </c>
-      <c r="J90" s="7">
+      <c r="K90" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="91" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L90" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="14.25" customHeight="1">
       <c r="A91" s="4" t="s">
         <v>22</v>
       </c>
@@ -2919,20 +3290,24 @@
       <c r="D91" s="3">
         <v>70</v>
       </c>
-      <c r="E91" s="11"/>
-      <c r="F91" s="12"/>
-      <c r="G91" s="11">
+      <c r="E91" s="12"/>
+      <c r="F91" s="13"/>
+      <c r="G91" s="12">
         <v>70</v>
       </c>
-      <c r="H91" s="12"/>
-      <c r="I91" s="7">
+      <c r="H91" s="13"/>
+      <c r="I91" s="10"/>
+      <c r="J91" s="7">
         <v>50</v>
       </c>
-      <c r="J91" s="7">
+      <c r="K91" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L91" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="14.25" customHeight="1">
       <c r="A92" s="4" t="s">
         <v>22</v>
       </c>
@@ -2945,20 +3320,24 @@
       <c r="D92" s="3">
         <v>127</v>
       </c>
-      <c r="E92" s="11"/>
-      <c r="F92" s="12"/>
-      <c r="G92" s="11">
+      <c r="E92" s="12"/>
+      <c r="F92" s="13"/>
+      <c r="G92" s="12">
         <v>127</v>
       </c>
-      <c r="H92" s="12"/>
-      <c r="I92" s="7">
+      <c r="H92" s="13"/>
+      <c r="I92" s="10"/>
+      <c r="J92" s="7">
         <v>50</v>
       </c>
-      <c r="J92" s="7">
+      <c r="K92" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="93" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L92" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="14.25" customHeight="1">
       <c r="A93" s="4" t="s">
         <v>22</v>
       </c>
@@ -2971,20 +3350,24 @@
       <c r="D93" s="3">
         <v>127</v>
       </c>
-      <c r="E93" s="11"/>
-      <c r="F93" s="12"/>
-      <c r="G93" s="11">
+      <c r="E93" s="12"/>
+      <c r="F93" s="13"/>
+      <c r="G93" s="12">
         <v>127</v>
       </c>
-      <c r="H93" s="12"/>
-      <c r="I93" s="7">
+      <c r="H93" s="13"/>
+      <c r="I93" s="10"/>
+      <c r="J93" s="7">
         <v>50</v>
       </c>
-      <c r="J93" s="7">
+      <c r="K93" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="94" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L93" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="14.25" customHeight="1">
       <c r="A94" s="4" t="s">
         <v>22</v>
       </c>
@@ -2997,20 +3380,24 @@
       <c r="D94" s="3">
         <v>66</v>
       </c>
-      <c r="E94" s="11"/>
-      <c r="F94" s="12"/>
-      <c r="G94" s="11">
+      <c r="E94" s="12"/>
+      <c r="F94" s="13"/>
+      <c r="G94" s="12">
         <v>66</v>
       </c>
-      <c r="H94" s="12"/>
-      <c r="I94" s="7">
+      <c r="H94" s="13"/>
+      <c r="I94" s="10"/>
+      <c r="J94" s="7">
         <v>50</v>
       </c>
-      <c r="J94" s="7">
+      <c r="K94" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L94" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="14.25" customHeight="1">
       <c r="A95" s="4" t="s">
         <v>22</v>
       </c>
@@ -3023,20 +3410,24 @@
       <c r="D95" s="3">
         <v>66</v>
       </c>
-      <c r="E95" s="11"/>
-      <c r="F95" s="12"/>
-      <c r="G95" s="11">
+      <c r="E95" s="12"/>
+      <c r="F95" s="13"/>
+      <c r="G95" s="12">
         <v>66</v>
       </c>
-      <c r="H95" s="12"/>
-      <c r="I95" s="7">
+      <c r="H95" s="13"/>
+      <c r="I95" s="10"/>
+      <c r="J95" s="7">
         <v>55</v>
       </c>
-      <c r="J95" s="7">
+      <c r="K95" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="96" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L95" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="14.25" customHeight="1">
       <c r="A96" s="4" t="s">
         <v>22</v>
       </c>
@@ -3049,20 +3440,24 @@
       <c r="D96" s="3">
         <v>79</v>
       </c>
-      <c r="E96" s="11"/>
-      <c r="F96" s="12"/>
-      <c r="G96" s="11">
+      <c r="E96" s="12"/>
+      <c r="F96" s="13"/>
+      <c r="G96" s="12">
         <v>79</v>
       </c>
-      <c r="H96" s="12"/>
-      <c r="I96" s="7">
+      <c r="H96" s="13"/>
+      <c r="I96" s="10"/>
+      <c r="J96" s="7">
         <v>55</v>
       </c>
-      <c r="J96" s="7">
+      <c r="K96" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="97" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L96" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="14.25" customHeight="1">
       <c r="A97" s="4" t="s">
         <v>22</v>
       </c>
@@ -3075,20 +3470,24 @@
       <c r="D97" s="3">
         <v>140</v>
       </c>
-      <c r="E97" s="11"/>
-      <c r="F97" s="12"/>
-      <c r="G97" s="11">
+      <c r="E97" s="12"/>
+      <c r="F97" s="13"/>
+      <c r="G97" s="12">
         <v>140</v>
       </c>
-      <c r="H97" s="12"/>
-      <c r="I97" s="7">
+      <c r="H97" s="13"/>
+      <c r="I97" s="10"/>
+      <c r="J97" s="7">
         <v>55</v>
       </c>
-      <c r="J97" s="7">
+      <c r="K97" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L97" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="14.25" customHeight="1">
       <c r="A98" s="4" t="s">
         <v>22</v>
       </c>
@@ -3101,20 +3500,24 @@
       <c r="D98" s="3">
         <v>140</v>
       </c>
-      <c r="E98" s="11"/>
-      <c r="F98" s="12"/>
-      <c r="G98" s="11">
+      <c r="E98" s="12"/>
+      <c r="F98" s="13"/>
+      <c r="G98" s="12">
         <v>140</v>
       </c>
-      <c r="H98" s="12"/>
-      <c r="I98" s="7">
+      <c r="H98" s="13"/>
+      <c r="I98" s="10"/>
+      <c r="J98" s="7">
         <v>55</v>
       </c>
-      <c r="J98" s="7">
+      <c r="K98" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="99" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L98" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="14.25" customHeight="1">
       <c r="A99" s="4" t="s">
         <v>22</v>
       </c>
@@ -3127,20 +3530,24 @@
       <c r="D99" s="3">
         <v>115</v>
       </c>
-      <c r="E99" s="11"/>
-      <c r="F99" s="12"/>
-      <c r="G99" s="11">
+      <c r="E99" s="12"/>
+      <c r="F99" s="13"/>
+      <c r="G99" s="12">
         <v>115</v>
       </c>
-      <c r="H99" s="12"/>
-      <c r="I99" s="7">
+      <c r="H99" s="13"/>
+      <c r="I99" s="10"/>
+      <c r="J99" s="7">
         <v>55</v>
       </c>
-      <c r="J99" s="7">
+      <c r="K99" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L99" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="14.25" customHeight="1">
       <c r="A100" s="4" t="s">
         <v>22</v>
       </c>
@@ -3153,20 +3560,24 @@
       <c r="D100" s="3">
         <v>88</v>
       </c>
-      <c r="E100" s="11"/>
-      <c r="F100" s="12"/>
-      <c r="G100" s="11">
+      <c r="E100" s="12"/>
+      <c r="F100" s="13"/>
+      <c r="G100" s="12">
         <v>88</v>
       </c>
-      <c r="H100" s="12"/>
-      <c r="I100" s="7">
+      <c r="H100" s="13"/>
+      <c r="I100" s="10"/>
+      <c r="J100" s="7">
         <v>55</v>
       </c>
-      <c r="J100" s="7">
+      <c r="K100" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L100" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="14.25" customHeight="1">
       <c r="A101" s="4" t="s">
         <v>22</v>
       </c>
@@ -3179,20 +3590,24 @@
       <c r="D101" s="3">
         <v>66</v>
       </c>
-      <c r="E101" s="11"/>
-      <c r="F101" s="12"/>
-      <c r="G101" s="11">
+      <c r="E101" s="12"/>
+      <c r="F101" s="13"/>
+      <c r="G101" s="12">
         <v>66</v>
       </c>
-      <c r="H101" s="12"/>
-      <c r="I101" s="7">
+      <c r="H101" s="13"/>
+      <c r="I101" s="10"/>
+      <c r="J101" s="7">
         <v>55</v>
       </c>
-      <c r="J101" s="7">
+      <c r="K101" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L101" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="14.25" customHeight="1">
       <c r="A102" s="4" t="s">
         <v>22</v>
       </c>
@@ -3205,20 +3620,24 @@
       <c r="D102" s="3">
         <v>66</v>
       </c>
-      <c r="E102" s="11"/>
-      <c r="F102" s="12"/>
-      <c r="G102" s="11">
+      <c r="E102" s="12"/>
+      <c r="F102" s="13"/>
+      <c r="G102" s="12">
         <v>66</v>
       </c>
-      <c r="H102" s="12"/>
-      <c r="I102" s="7">
+      <c r="H102" s="13"/>
+      <c r="I102" s="10"/>
+      <c r="J102" s="7">
         <v>55</v>
       </c>
-      <c r="J102" s="7">
+      <c r="K102" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="103" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L102" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="14.25" customHeight="1">
       <c r="A103" s="4" t="s">
         <v>22</v>
       </c>
@@ -3231,20 +3650,24 @@
       <c r="D103" s="3">
         <v>77</v>
       </c>
-      <c r="E103" s="11"/>
-      <c r="F103" s="12"/>
-      <c r="G103" s="11">
+      <c r="E103" s="12"/>
+      <c r="F103" s="13"/>
+      <c r="G103" s="12">
         <v>77</v>
       </c>
-      <c r="H103" s="12"/>
-      <c r="I103" s="7">
+      <c r="H103" s="13"/>
+      <c r="I103" s="10"/>
+      <c r="J103" s="7">
         <v>55</v>
       </c>
-      <c r="J103" s="7">
+      <c r="K103" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L103" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="14.25" customHeight="1">
       <c r="A104" s="4" t="s">
         <v>22</v>
       </c>
@@ -3257,20 +3680,24 @@
       <c r="D104" s="3">
         <v>140</v>
       </c>
-      <c r="E104" s="11"/>
-      <c r="F104" s="12"/>
-      <c r="G104" s="11">
+      <c r="E104" s="12"/>
+      <c r="F104" s="13"/>
+      <c r="G104" s="12">
         <v>140</v>
       </c>
-      <c r="H104" s="12"/>
-      <c r="I104" s="7">
+      <c r="H104" s="13"/>
+      <c r="I104" s="10"/>
+      <c r="J104" s="7">
         <v>55</v>
       </c>
-      <c r="J104" s="7">
+      <c r="K104" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="105" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L104" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="14.25" customHeight="1">
       <c r="A105" s="4" t="s">
         <v>22</v>
       </c>
@@ -3283,20 +3710,24 @@
       <c r="D105" s="3">
         <v>140</v>
       </c>
-      <c r="E105" s="11"/>
-      <c r="F105" s="12"/>
-      <c r="G105" s="11">
+      <c r="E105" s="12"/>
+      <c r="F105" s="13"/>
+      <c r="G105" s="12">
         <v>140</v>
       </c>
-      <c r="H105" s="12"/>
-      <c r="I105" s="7">
+      <c r="H105" s="13"/>
+      <c r="I105" s="10"/>
+      <c r="J105" s="7">
         <v>55</v>
       </c>
-      <c r="J105" s="7">
+      <c r="K105" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="106" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L105" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="14.25" customHeight="1">
       <c r="A106" s="4" t="s">
         <v>22</v>
       </c>
@@ -3309,20 +3740,24 @@
       <c r="D106" s="3">
         <v>73</v>
       </c>
-      <c r="E106" s="11"/>
-      <c r="F106" s="12"/>
-      <c r="G106" s="11">
+      <c r="E106" s="12"/>
+      <c r="F106" s="13"/>
+      <c r="G106" s="12">
         <v>73</v>
       </c>
-      <c r="H106" s="12"/>
-      <c r="I106" s="7">
+      <c r="H106" s="13"/>
+      <c r="I106" s="10"/>
+      <c r="J106" s="7">
         <v>55</v>
       </c>
-      <c r="J106" s="7">
+      <c r="K106" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="107" spans="1:10" ht="14.25" customHeight="1">
+      <c r="L106" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="14.25" customHeight="1">
       <c r="A107" s="4" t="s">
         <v>23</v>
       </c>
@@ -3335,20 +3770,24 @@
       <c r="D107" s="3">
         <v>69</v>
       </c>
-      <c r="E107" s="11"/>
-      <c r="F107" s="12"/>
-      <c r="G107" s="11">
+      <c r="E107" s="12"/>
+      <c r="F107" s="13"/>
+      <c r="G107" s="12">
         <v>69</v>
       </c>
-      <c r="H107" s="12"/>
-      <c r="I107" s="7">
+      <c r="H107" s="13"/>
+      <c r="I107" s="10"/>
+      <c r="J107" s="7">
         <v>55</v>
       </c>
-      <c r="J107" s="7">
+      <c r="K107" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="108" spans="1:10">
+      <c r="L107" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12">
       <c r="A108" s="4" t="s">
         <v>23</v>
       </c>
@@ -3361,20 +3800,24 @@
       <c r="D108" s="3">
         <v>101</v>
       </c>
-      <c r="E108" s="11"/>
-      <c r="F108" s="12"/>
-      <c r="G108" s="11">
+      <c r="E108" s="12"/>
+      <c r="F108" s="13"/>
+      <c r="G108" s="12">
         <v>95</v>
       </c>
-      <c r="H108" s="12"/>
-      <c r="I108" s="7">
+      <c r="H108" s="13"/>
+      <c r="I108" s="10"/>
+      <c r="J108" s="7">
         <v>55</v>
       </c>
-      <c r="J108" s="7">
+      <c r="K108" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="109" spans="1:10">
+      <c r="L108" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12">
       <c r="A109" s="4" t="s">
         <v>23</v>
       </c>
@@ -3387,20 +3830,24 @@
       <c r="D109" s="3">
         <v>136</v>
       </c>
-      <c r="E109" s="11"/>
-      <c r="F109" s="12"/>
-      <c r="G109" s="11">
+      <c r="E109" s="12"/>
+      <c r="F109" s="13"/>
+      <c r="G109" s="12">
         <v>115</v>
       </c>
-      <c r="H109" s="12"/>
-      <c r="I109" s="7">
+      <c r="H109" s="13"/>
+      <c r="I109" s="10"/>
+      <c r="J109" s="7">
         <v>55</v>
       </c>
-      <c r="J109" s="7">
+      <c r="K109" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="110" spans="1:10">
+      <c r="L109" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12">
       <c r="A110" s="4" t="s">
         <v>23</v>
       </c>
@@ -3413,20 +3860,24 @@
       <c r="D110" s="3">
         <v>101</v>
       </c>
-      <c r="E110" s="11"/>
-      <c r="F110" s="12"/>
-      <c r="G110" s="11">
+      <c r="E110" s="12"/>
+      <c r="F110" s="13"/>
+      <c r="G110" s="12">
         <v>95</v>
       </c>
-      <c r="H110" s="12"/>
-      <c r="I110" s="7">
+      <c r="H110" s="13"/>
+      <c r="I110" s="10"/>
+      <c r="J110" s="7">
         <v>55</v>
       </c>
-      <c r="J110" s="7">
+      <c r="K110" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="111" spans="1:10">
+      <c r="L110" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12">
       <c r="A111" s="4" t="s">
         <v>23</v>
       </c>
@@ -3439,166 +3890,63 @@
       <c r="D111" s="3">
         <v>136</v>
       </c>
-      <c r="E111" s="11"/>
-      <c r="F111" s="12"/>
-      <c r="G111" s="11">
+      <c r="E111" s="12"/>
+      <c r="F111" s="13"/>
+      <c r="G111" s="12">
         <v>115</v>
       </c>
-      <c r="H111" s="12"/>
-      <c r="I111" s="7">
+      <c r="H111" s="13"/>
+      <c r="I111" s="10"/>
+      <c r="J111" s="7">
         <v>55</v>
       </c>
-      <c r="J111" s="7">
+      <c r="K111" s="7">
         <v>8</v>
+      </c>
+      <c r="L111" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="204">
-    <mergeCell ref="G109:H109"/>
-    <mergeCell ref="E109:F109"/>
-    <mergeCell ref="G110:H110"/>
-    <mergeCell ref="E110:F110"/>
-    <mergeCell ref="G111:H111"/>
-    <mergeCell ref="E111:F111"/>
-    <mergeCell ref="G106:H106"/>
-    <mergeCell ref="E106:F106"/>
-    <mergeCell ref="G107:H107"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="G108:H108"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="G104:H104"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="G105:H105"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="E99:F99"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="G96:H96"/>
-    <mergeCell ref="E96:F96"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="E97:F97"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="E100:F100"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="E98:F98"/>
-    <mergeCell ref="G93:H93"/>
-    <mergeCell ref="E93:F93"/>
-    <mergeCell ref="G94:H94"/>
-    <mergeCell ref="E94:F94"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="E95:F95"/>
-    <mergeCell ref="G90:H90"/>
-    <mergeCell ref="E90:F90"/>
-    <mergeCell ref="G91:H91"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="G92:H92"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="G87:H87"/>
-    <mergeCell ref="G88:H88"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="E88:F88"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="G85:H85"/>
-    <mergeCell ref="E85:F85"/>
-    <mergeCell ref="G86:H86"/>
-    <mergeCell ref="E86:F86"/>
-    <mergeCell ref="E84:F84"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="E80:F80"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="E81:F81"/>
-    <mergeCell ref="G82:H82"/>
-    <mergeCell ref="E82:F82"/>
-    <mergeCell ref="G77:H77"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="G78:H78"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="G79:H79"/>
-    <mergeCell ref="E79:F79"/>
-    <mergeCell ref="G74:H74"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="G75:H75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="G76:H76"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="G72:H72"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="G73:H73"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="G68:H68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="G69:H69"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="G67:H67"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="G63:H63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="G61:H61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G22:H22"/>
     <mergeCell ref="G34:H34"/>
     <mergeCell ref="E34:F34"/>
     <mergeCell ref="G36:H36"/>
@@ -3620,44 +3968,151 @@
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="G61:H61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="G72:H72"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="G77:H77"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="G79:H79"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="G76:H76"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="G85:H85"/>
+    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="E86:F86"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="G91:H91"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="G92:H92"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="G87:H87"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="G96:H96"/>
+    <mergeCell ref="E96:F96"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="E97:F97"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="E100:F100"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="E98:F98"/>
+    <mergeCell ref="G93:H93"/>
+    <mergeCell ref="E93:F93"/>
+    <mergeCell ref="G94:H94"/>
+    <mergeCell ref="E94:F94"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="G104:H104"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="G105:H105"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="G109:H109"/>
+    <mergeCell ref="E109:F109"/>
+    <mergeCell ref="G110:H110"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="G111:H111"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="G106:H106"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="G107:H107"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="G108:H108"/>
+    <mergeCell ref="E108:F108"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
